--- a/deuda-interna/deuda_interna_resumen.xlsx
+++ b/deuda-interna/deuda_interna_resumen.xlsx
@@ -604,7 +604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 22-Aug-2026  ·  Fuente: Bolsa de Valores de Quito</t>
+          <t>Generado: 12-Sep-2026  ·  Fuente: Bolsa de Valores de Quito</t>
         </is>
       </c>
     </row>
@@ -845,34 +845,34 @@
         <v>2026</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1930761460.400001</v>
+        <v>1970002216.109999</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>543538968.99</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1314172597.270001</v>
+        <v>1350282301.89</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>48613140.7</v>
+        <v>51407640.21999999</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>24436753.44</v>
+        <v>24773305.01</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>28.15153400034169</v>
+        <v>27.5907795709632</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>68.06499012041293</v>
+        <v>68.54217172183141</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>2.51782220108789</v>
+        <v>2.609521948737215</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1.265653678157496</v>
+        <v>1.257526758468211</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>7.672456521739131</v>
+        <v>7.74459457364341</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>4379404303.27</v>
+        <v>4418645058.979999</v>
       </c>
       <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2375,19 +2375,44 @@
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>58115367.70999998</v>
+        <v>63187085.14999998</v>
       </c>
       <c r="D59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>55021345.66999998</v>
+        <v>57353563.75999998</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>3094022.04</v>
+        <v>5833521.390000001</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>34169038.27000003</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>33777486.53000002</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>55000.17000000001</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>336551.57</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3938,16 +3963,38 @@
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>5.9388</v>
+        <v>5.7535</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>7.8191</v>
+        <v>7.6667</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>8.4499</v>
+        <v>8.416499999999999</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>9.294499999999999</v>
+        <v>9.2264</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>4.8417</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>7.5018</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>8.331300000000001</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>9.047599999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3964,7 +4011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1273"/>
+  <dimension ref="A1:N1352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -72672,6 +72719,4272 @@
         </is>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1274" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1274" s="24" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D1274" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1274" s="25" t="n">
+        <v>100.000012</v>
+      </c>
+      <c r="F1274" s="25" t="n">
+        <v>8.115500000000001</v>
+      </c>
+      <c r="G1274" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1274" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1274" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J1274" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1274" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1274" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1274" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1274" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1275" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1275" s="20" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D1275" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1275" s="21" t="n">
+        <v>100.000012</v>
+      </c>
+      <c r="F1275" s="21" t="n">
+        <v>8.115500000000001</v>
+      </c>
+      <c r="G1275" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1275" s="22" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I1275" s="22" t="n">
+        <v>60000.01</v>
+      </c>
+      <c r="J1275" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1275" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1275" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1275" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1275" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1276" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1276" s="24" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D1276" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1276" s="25" t="n">
+        <v>100.000336</v>
+      </c>
+      <c r="F1276" s="25" t="n">
+        <v>8.2874</v>
+      </c>
+      <c r="G1276" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1276" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1276" s="26" t="n">
+        <v>15000.05</v>
+      </c>
+      <c r="J1276" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1276" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1276" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1276" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1276" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1277" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1277" s="20" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D1277" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1277" s="21" t="n">
+        <v>100.000012</v>
+      </c>
+      <c r="F1277" s="21" t="n">
+        <v>8.115500000000001</v>
+      </c>
+      <c r="G1277" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1277" s="22" t="n">
+        <v>92262</v>
+      </c>
+      <c r="I1277" s="22" t="n">
+        <v>92262.00999999999</v>
+      </c>
+      <c r="J1277" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1277" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1277" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1277" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1277" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1278" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1278" s="24" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D1278" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1278" s="25" t="n">
+        <v>100.00022</v>
+      </c>
+      <c r="F1278" s="25" t="n">
+        <v>8.1153</v>
+      </c>
+      <c r="G1278" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1278" s="26" t="n">
+        <v>360000</v>
+      </c>
+      <c r="I1278" s="26" t="n">
+        <v>360000.79</v>
+      </c>
+      <c r="J1278" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1278" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1278" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1278" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1278" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="19" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1279" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1279" s="20" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D1279" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1279" s="21" t="n">
+        <v>100.00022</v>
+      </c>
+      <c r="F1279" s="21" t="n">
+        <v>8.1153</v>
+      </c>
+      <c r="G1279" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1279" s="22" t="n">
+        <v>663000</v>
+      </c>
+      <c r="I1279" s="22" t="n">
+        <v>663001.46</v>
+      </c>
+      <c r="J1279" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1279" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1279" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1279" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1279" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1280" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1280" s="24" t="n">
+        <v>1774</v>
+      </c>
+      <c r="D1280" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1280" s="25" t="n">
+        <v>99.99999800000001</v>
+      </c>
+      <c r="F1280" s="25" t="n">
+        <v>8.2874</v>
+      </c>
+      <c r="G1280" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1280" s="26" t="n">
+        <v>31000</v>
+      </c>
+      <c r="I1280" s="26" t="n">
+        <v>31000</v>
+      </c>
+      <c r="J1280" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1280" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1280" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1280" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1280" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="19" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1281" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1281" s="20" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D1281" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1281" s="21" t="n">
+        <v>100.00022</v>
+      </c>
+      <c r="F1281" s="21" t="n">
+        <v>8.1153</v>
+      </c>
+      <c r="G1281" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1281" s="22" t="n">
+        <v>83583</v>
+      </c>
+      <c r="I1281" s="22" t="n">
+        <v>83583.17999999999</v>
+      </c>
+      <c r="J1281" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1281" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1281" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1281" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1281" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="23" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1282" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1282" s="24" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D1282" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1282" s="25" t="n">
+        <v>100.000062</v>
+      </c>
+      <c r="F1282" s="25" t="n">
+        <v>8.2873</v>
+      </c>
+      <c r="G1282" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1282" s="26" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I1282" s="26" t="n">
+        <v>1000000.62</v>
+      </c>
+      <c r="J1282" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1282" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1282" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1282" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1282" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="19" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1283" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1283" s="20" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D1283" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1283" s="21" t="n">
+        <v>100.000062</v>
+      </c>
+      <c r="F1283" s="21" t="n">
+        <v>8.2873</v>
+      </c>
+      <c r="G1283" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1283" s="22" t="n">
+        <v>118493</v>
+      </c>
+      <c r="I1283" s="22" t="n">
+        <v>118493.07</v>
+      </c>
+      <c r="J1283" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1283" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1283" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1283" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1283" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="23" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1284" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1284" s="24" t="n">
+        <v>1046</v>
+      </c>
+      <c r="D1284" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1284" s="25" t="n">
+        <v>100.000141</v>
+      </c>
+      <c r="F1284" s="25" t="n">
+        <v>8.1151</v>
+      </c>
+      <c r="G1284" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1284" s="26" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I1284" s="26" t="n">
+        <v>16000.02</v>
+      </c>
+      <c r="J1284" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1284" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1284" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1284" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1284" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="19" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1285" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1285" s="20" t="n">
+        <v>1772</v>
+      </c>
+      <c r="D1285" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1285" s="21" t="n">
+        <v>100.000131</v>
+      </c>
+      <c r="F1285" s="21" t="n">
+        <v>8.2872</v>
+      </c>
+      <c r="G1285" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1285" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1285" s="22" t="n">
+        <v>30000.04</v>
+      </c>
+      <c r="J1285" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1285" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1285" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1285" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1285" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1286" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1286" s="24" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D1286" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1286" s="25" t="n">
+        <v>100.000109</v>
+      </c>
+      <c r="F1286" s="25" t="n">
+        <v>8.115</v>
+      </c>
+      <c r="G1286" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1286" s="26" t="n">
+        <v>27630</v>
+      </c>
+      <c r="I1286" s="26" t="n">
+        <v>27630.03</v>
+      </c>
+      <c r="J1286" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1286" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1286" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1286" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1286" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="19" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1287" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1287" s="20" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D1287" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1287" s="21" t="n">
+        <v>100.000109</v>
+      </c>
+      <c r="F1287" s="21" t="n">
+        <v>8.115</v>
+      </c>
+      <c r="G1287" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1287" s="22" t="n">
+        <v>14740</v>
+      </c>
+      <c r="I1287" s="22" t="n">
+        <v>14740.02</v>
+      </c>
+      <c r="J1287" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1287" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1287" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1287" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1287" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1288" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1288" s="24" t="n">
+        <v>1771</v>
+      </c>
+      <c r="D1288" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1288" s="25" t="n">
+        <v>100.000204</v>
+      </c>
+      <c r="F1288" s="25" t="n">
+        <v>8.287100000000001</v>
+      </c>
+      <c r="G1288" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1288" s="26" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I1288" s="26" t="n">
+        <v>45000.09</v>
+      </c>
+      <c r="J1288" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1288" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1288" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1288" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1288" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="19" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1289" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1289" s="20" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D1289" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1289" s="21" t="n">
+        <v>100.000366</v>
+      </c>
+      <c r="F1289" s="21" t="n">
+        <v>8.286899999999999</v>
+      </c>
+      <c r="G1289" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1289" s="22" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I1289" s="22" t="n">
+        <v>400001.46</v>
+      </c>
+      <c r="J1289" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1289" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1289" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1289" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1289" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1290" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1290" s="24" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D1290" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1290" s="25" t="n">
+        <v>100.000366</v>
+      </c>
+      <c r="F1290" s="25" t="n">
+        <v>8.286899999999999</v>
+      </c>
+      <c r="G1290" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1290" s="26" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I1290" s="26" t="n">
+        <v>400001.46</v>
+      </c>
+      <c r="J1290" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1290" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1290" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1290" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1290" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="19" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1291" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1291" s="20" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D1291" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1291" s="21" t="n">
+        <v>100.000366</v>
+      </c>
+      <c r="F1291" s="21" t="n">
+        <v>8.286899999999999</v>
+      </c>
+      <c r="G1291" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1291" s="22" t="n">
+        <v>700000</v>
+      </c>
+      <c r="I1291" s="22" t="n">
+        <v>700002.5600000001</v>
+      </c>
+      <c r="J1291" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1291" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1291" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1291" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1291" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1292" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1292" s="24" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D1292" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1292" s="25" t="n">
+        <v>100.000057</v>
+      </c>
+      <c r="F1292" s="25" t="n">
+        <v>8.114800000000001</v>
+      </c>
+      <c r="G1292" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1292" s="26" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I1292" s="26" t="n">
+        <v>600000.34</v>
+      </c>
+      <c r="J1292" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1292" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1292" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1292" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1292" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="19" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1293" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1293" s="20" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D1293" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1293" s="21" t="n">
+        <v>100.000057</v>
+      </c>
+      <c r="F1293" s="21" t="n">
+        <v>8.114800000000001</v>
+      </c>
+      <c r="G1293" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1293" s="22" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I1293" s="22" t="n">
+        <v>400000.23</v>
+      </c>
+      <c r="J1293" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1293" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1293" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1293" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1293" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1294" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1294" s="24" t="n">
+        <v>1042</v>
+      </c>
+      <c r="D1294" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1294" s="25" t="n">
+        <v>100.000038</v>
+      </c>
+      <c r="F1294" s="25" t="n">
+        <v>8.114699999999999</v>
+      </c>
+      <c r="G1294" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1294" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1294" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J1294" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1294" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1294" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1294" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1294" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="19" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1295" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1295" s="20" t="n">
+        <v>1042</v>
+      </c>
+      <c r="D1295" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1295" s="21" t="n">
+        <v>100.000038</v>
+      </c>
+      <c r="F1295" s="21" t="n">
+        <v>8.114699999999999</v>
+      </c>
+      <c r="G1295" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1295" s="22" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I1295" s="22" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J1295" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1295" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1295" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1295" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1295" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1296" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1296" s="24" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D1296" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1296" s="25" t="n">
+        <v>100.000023</v>
+      </c>
+      <c r="F1296" s="25" t="n">
+        <v>8.114599999999999</v>
+      </c>
+      <c r="G1296" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1296" s="26" t="n">
+        <v>33600</v>
+      </c>
+      <c r="I1296" s="26" t="n">
+        <v>33600.01</v>
+      </c>
+      <c r="J1296" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1296" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1296" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1296" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1296" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1297" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1297" s="20" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D1297" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1297" s="21" t="n">
+        <v>100.000023</v>
+      </c>
+      <c r="F1297" s="21" t="n">
+        <v>8.114599999999999</v>
+      </c>
+      <c r="G1297" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1297" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I1297" s="22" t="n">
+        <v>1500000.34</v>
+      </c>
+      <c r="J1297" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1297" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1297" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1297" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1297" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1298" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1298" s="24" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D1298" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1298" s="25" t="n">
+        <v>100.000023</v>
+      </c>
+      <c r="F1298" s="25" t="n">
+        <v>8.114599999999999</v>
+      </c>
+      <c r="G1298" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1298" s="26" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I1298" s="26" t="n">
+        <v>1500000.34</v>
+      </c>
+      <c r="J1298" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1298" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1298" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1298" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1298" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="19" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1299" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1299" s="20" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D1299" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1299" s="21" t="n">
+        <v>100.000023</v>
+      </c>
+      <c r="F1299" s="21" t="n">
+        <v>8.114599999999999</v>
+      </c>
+      <c r="G1299" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1299" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I1299" s="22" t="n">
+        <v>1500000.34</v>
+      </c>
+      <c r="J1299" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1299" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1299" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1299" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1299" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1300" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1300" s="24" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D1300" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1300" s="25" t="n">
+        <v>100.000013</v>
+      </c>
+      <c r="F1300" s="25" t="n">
+        <v>8.1145</v>
+      </c>
+      <c r="G1300" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1300" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1300" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J1300" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1300" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1300" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1300" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1300" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1301" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1301" s="20" t="n">
+        <v>2404</v>
+      </c>
+      <c r="D1301" s="15" t="inlineStr">
+        <is>
+          <t>Mas de 5</t>
+        </is>
+      </c>
+      <c r="E1301" s="21" t="n">
+        <v>100.000466</v>
+      </c>
+      <c r="F1301" s="21" t="n">
+        <v>8.366</v>
+      </c>
+      <c r="G1301" s="21" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H1301" s="22" t="n">
+        <v>336550</v>
+      </c>
+      <c r="I1301" s="22" t="n">
+        <v>336551.57</v>
+      </c>
+      <c r="J1301" s="19" t="n">
+        <v>46149</v>
+      </c>
+      <c r="K1301" s="19" t="n">
+        <v>48706</v>
+      </c>
+      <c r="L1301" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1301" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1301" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1302" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1302" s="24" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D1302" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1302" s="25" t="n">
+        <v>100.000013</v>
+      </c>
+      <c r="F1302" s="25" t="n">
+        <v>8.1145</v>
+      </c>
+      <c r="G1302" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1302" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1302" s="26" t="n">
+        <v>500000.06</v>
+      </c>
+      <c r="J1302" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1302" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1302" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1302" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1302" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1303" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1303" s="20" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D1303" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1303" s="21" t="n">
+        <v>100.000013</v>
+      </c>
+      <c r="F1303" s="21" t="n">
+        <v>8.1145</v>
+      </c>
+      <c r="G1303" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1303" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1303" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J1303" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1303" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1303" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1303" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1303" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1304" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1304" s="24" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1304" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1304" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1304" s="25" t="n">
+        <v>8.1144</v>
+      </c>
+      <c r="G1304" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1304" s="26" t="n">
+        <v>3859202.92</v>
+      </c>
+      <c r="I1304" s="26" t="n">
+        <v>3859203.18</v>
+      </c>
+      <c r="J1304" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1304" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1304" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1304" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1304" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1305" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1305" s="20" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D1305" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1305" s="21" t="n">
+        <v>100.000017</v>
+      </c>
+      <c r="F1305" s="21" t="n">
+        <v>8.114100000000001</v>
+      </c>
+      <c r="G1305" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1305" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1305" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J1305" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1305" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1305" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1305" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1305" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1306" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1306" s="24" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1306" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1306" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1306" s="25" t="n">
+        <v>8.1144</v>
+      </c>
+      <c r="G1306" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1306" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1306" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J1306" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1306" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1306" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1306" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1306" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1307" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1307" s="20" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D1307" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1307" s="21" t="n">
+        <v>100.00035</v>
+      </c>
+      <c r="F1307" s="21" t="n">
+        <v>8.2866</v>
+      </c>
+      <c r="G1307" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1307" s="22" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I1307" s="22" t="n">
+        <v>43000.15</v>
+      </c>
+      <c r="J1307" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1307" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1307" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1307" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1307" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1308" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1308" s="24" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1308" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1308" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1308" s="25" t="n">
+        <v>8.1144</v>
+      </c>
+      <c r="G1308" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1308" s="26" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I1308" s="26" t="n">
+        <v>800000.05</v>
+      </c>
+      <c r="J1308" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1308" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1308" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1308" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1308" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1309" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1309" s="20" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D1309" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1309" s="21" t="n">
+        <v>100.000017</v>
+      </c>
+      <c r="F1309" s="21" t="n">
+        <v>8.114100000000001</v>
+      </c>
+      <c r="G1309" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1309" s="22" t="n">
+        <v>36550</v>
+      </c>
+      <c r="I1309" s="22" t="n">
+        <v>36550.01</v>
+      </c>
+      <c r="J1309" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1309" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1309" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1309" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1309" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1310" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1310" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1310" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1310" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1310" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1310" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1310" s="26" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I1310" s="26" t="n">
+        <v>6500001.88</v>
+      </c>
+      <c r="J1310" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1310" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1310" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1310" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1310" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1311" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1311" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1311" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1311" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1311" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1311" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1311" s="22" t="n">
+        <v>9860</v>
+      </c>
+      <c r="I1311" s="22" t="n">
+        <v>9860</v>
+      </c>
+      <c r="J1311" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1311" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1311" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1311" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1311" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1312" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1312" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1312" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1312" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1312" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1312" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1312" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1312" s="26" t="n">
+        <v>30000.01</v>
+      </c>
+      <c r="J1312" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1312" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1312" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1312" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1312" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1313" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1313" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1313" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1313" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1313" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1313" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1313" s="22" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I1313" s="22" t="n">
+        <v>100000.03</v>
+      </c>
+      <c r="J1313" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1313" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1313" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1313" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1313" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1314" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1314" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1314" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1314" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1314" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1314" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1314" s="26" t="n">
+        <v>17930</v>
+      </c>
+      <c r="I1314" s="26" t="n">
+        <v>17930.01</v>
+      </c>
+      <c r="J1314" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1314" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1314" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1314" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1314" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1315" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1315" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1315" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1315" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1315" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1315" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1315" s="22" t="n">
+        <v>1148289</v>
+      </c>
+      <c r="I1315" s="22" t="n">
+        <v>1148289.33</v>
+      </c>
+      <c r="J1315" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1315" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1315" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1315" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1315" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1316" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1316" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1316" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1316" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1316" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1316" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1316" s="26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I1316" s="26" t="n">
+        <v>70000.02</v>
+      </c>
+      <c r="J1316" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1316" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1316" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1316" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1316" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1317" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1317" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1317" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1317" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1317" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1317" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1317" s="22" t="n">
+        <v>15140</v>
+      </c>
+      <c r="I1317" s="22" t="n">
+        <v>15140</v>
+      </c>
+      <c r="J1317" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1317" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1317" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1317" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1317" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1318" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1318" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1318" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1318" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1318" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1318" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1318" s="26" t="n">
+        <v>14100</v>
+      </c>
+      <c r="I1318" s="26" t="n">
+        <v>14100</v>
+      </c>
+      <c r="J1318" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1318" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1318" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1318" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1318" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1319" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1319" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1319" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1319" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1319" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1319" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1319" s="22" t="n">
+        <v>54000</v>
+      </c>
+      <c r="I1319" s="22" t="n">
+        <v>54000.02</v>
+      </c>
+      <c r="J1319" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1319" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1319" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1319" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1319" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1320" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1320" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1320" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1320" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1320" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1320" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1320" s="26" t="n">
+        <v>76615</v>
+      </c>
+      <c r="I1320" s="26" t="n">
+        <v>76615.02</v>
+      </c>
+      <c r="J1320" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1320" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1320" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1320" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1320" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="19" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1321" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1321" s="20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1321" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1321" s="21" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1321" s="21" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1321" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1321" s="22" t="n">
+        <v>54485</v>
+      </c>
+      <c r="I1321" s="22" t="n">
+        <v>54485.02</v>
+      </c>
+      <c r="J1321" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1321" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1321" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1321" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1321" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1322" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1322" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1322" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1322" s="25" t="n">
+        <v>100.000029</v>
+      </c>
+      <c r="F1322" s="25" t="n">
+        <v>8.114000000000001</v>
+      </c>
+      <c r="G1322" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1322" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1322" s="26" t="n">
+        <v>30000.01</v>
+      </c>
+      <c r="J1322" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1322" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1322" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1322" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1322" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1323" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1323" s="20" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1323" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1323" s="21" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1323" s="21" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1323" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1323" s="22" t="n">
+        <v>31900</v>
+      </c>
+      <c r="I1323" s="22" t="n">
+        <v>31900.01</v>
+      </c>
+      <c r="J1323" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1323" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1323" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1323" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1323" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1324" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1324" s="24" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1324" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1324" s="25" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1324" s="25" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1324" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1324" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1324" s="26" t="n">
+        <v>15000.01</v>
+      </c>
+      <c r="J1324" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1324" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1324" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1324" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1324" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1325" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1325" s="20" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1325" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1325" s="21" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1325" s="21" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1325" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1325" s="22" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1325" s="22" t="n">
+        <v>12000.01</v>
+      </c>
+      <c r="J1325" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1325" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1325" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1325" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1325" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1326" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1326" s="24" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1326" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1326" s="25" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1326" s="25" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1326" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1326" s="26" t="n">
+        <v>617229</v>
+      </c>
+      <c r="I1326" s="26" t="n">
+        <v>617229.28</v>
+      </c>
+      <c r="J1326" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1326" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1326" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1326" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1326" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1327" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1327" s="20" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D1327" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1327" s="21" t="n">
+        <v>100.000142</v>
+      </c>
+      <c r="F1327" s="21" t="n">
+        <v>8.286300000000001</v>
+      </c>
+      <c r="G1327" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1327" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1327" s="22" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1327" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1327" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1327" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1327" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1327" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1328" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1328" s="24" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D1328" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1328" s="25" t="n">
+        <v>100.000142</v>
+      </c>
+      <c r="F1328" s="25" t="n">
+        <v>8.286300000000001</v>
+      </c>
+      <c r="G1328" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1328" s="26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1328" s="26" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1328" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1328" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1328" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1328" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1328" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1329" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1329" s="20" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1329" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1329" s="21" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1329" s="21" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1329" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1329" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I1329" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J1329" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1329" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1329" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1329" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1329" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1330" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1330" s="24" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D1330" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1330" s="25" t="n">
+        <v>100.000046</v>
+      </c>
+      <c r="F1330" s="25" t="n">
+        <v>8.113899999999999</v>
+      </c>
+      <c r="G1330" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1330" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1330" s="26" t="n">
+        <v>30000.01</v>
+      </c>
+      <c r="J1330" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1330" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1330" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1330" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1330" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1331" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1331" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1331" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1331" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1331" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1331" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1331" s="22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1331" s="22" t="n">
+        <v>9000.01</v>
+      </c>
+      <c r="J1331" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1331" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1331" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1331" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1331" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1332" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1332" s="24" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1332" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1332" s="25" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1332" s="25" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1332" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1332" s="26" t="n">
+        <v>348180</v>
+      </c>
+      <c r="I1332" s="26" t="n">
+        <v>348180.23</v>
+      </c>
+      <c r="J1332" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1332" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1332" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1332" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1332" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1333" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1333" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1333" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1333" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1333" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1333" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1333" s="22" t="n">
+        <v>764936</v>
+      </c>
+      <c r="I1333" s="22" t="n">
+        <v>764936.51</v>
+      </c>
+      <c r="J1333" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1333" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1333" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1333" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1333" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1334" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1334" s="24" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1334" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1334" s="25" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1334" s="25" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1334" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1334" s="26" t="n">
+        <v>425685</v>
+      </c>
+      <c r="I1334" s="26" t="n">
+        <v>425685.28</v>
+      </c>
+      <c r="J1334" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1334" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1334" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1334" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1334" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1335" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1335" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1335" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1335" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1335" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1335" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1335" s="22" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I1335" s="22" t="n">
+        <v>5000003.35</v>
+      </c>
+      <c r="J1335" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1335" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1335" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1335" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1335" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1336" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1336" s="24" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1336" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1336" s="25" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1336" s="25" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1336" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1336" s="26" t="n">
+        <v>39270</v>
+      </c>
+      <c r="I1336" s="26" t="n">
+        <v>39270.03</v>
+      </c>
+      <c r="J1336" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1336" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1336" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1336" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1336" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1337" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1337" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1337" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1337" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1337" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1337" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1337" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I1337" s="22" t="n">
+        <v>25000.02</v>
+      </c>
+      <c r="J1337" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1337" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1337" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1337" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1337" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1338" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1338" s="24" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1338" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1338" s="25" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1338" s="25" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1338" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1338" s="26" t="n">
+        <v>5855153.74</v>
+      </c>
+      <c r="I1338" s="26" t="n">
+        <v>5855157.66</v>
+      </c>
+      <c r="J1338" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1338" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1338" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1338" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1338" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1339" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1339" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1339" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1339" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1339" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1339" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1339" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1339" s="22" t="n">
+        <v>20000.01</v>
+      </c>
+      <c r="J1339" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1339" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1339" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1339" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1339" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1340" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1340" s="24" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1340" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1340" s="25" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1340" s="25" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1340" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1340" s="26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I1340" s="26" t="n">
+        <v>150000.1</v>
+      </c>
+      <c r="J1340" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1340" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1340" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1340" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1340" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1341" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1341" s="20" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D1341" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1341" s="21" t="n">
+        <v>100.000067</v>
+      </c>
+      <c r="F1341" s="21" t="n">
+        <v>8.113799999999999</v>
+      </c>
+      <c r="G1341" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1341" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1341" s="22" t="n">
+        <v>30000.02</v>
+      </c>
+      <c r="J1341" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1341" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1341" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1341" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1341" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1342" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1342" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1342" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1342" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1342" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1342" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1342" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I1342" s="26" t="n">
+        <v>50000.05</v>
+      </c>
+      <c r="J1342" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1342" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1342" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1342" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1342" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1343" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1343" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1343" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1343" s="21" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1343" s="21" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1343" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1343" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1343" s="22" t="n">
+        <v>10000.01</v>
+      </c>
+      <c r="J1343" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1343" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1343" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1343" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1343" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1344" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1344" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1344" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1344" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1344" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1344" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1344" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1344" s="26" t="n">
+        <v>8000.01</v>
+      </c>
+      <c r="J1344" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1344" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1344" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1344" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1344" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1345" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1345" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1345" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1345" s="21" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1345" s="21" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1345" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1345" s="22" t="n">
+        <v>517135</v>
+      </c>
+      <c r="I1345" s="22" t="n">
+        <v>517135.48</v>
+      </c>
+      <c r="J1345" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1345" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1345" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1345" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1345" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1346" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1346" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1346" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1346" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1346" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1346" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1346" s="26" t="n">
+        <v>374046</v>
+      </c>
+      <c r="I1346" s="26" t="n">
+        <v>374046.35</v>
+      </c>
+      <c r="J1346" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1346" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1346" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1346" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1346" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1347" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1347" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1347" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1347" s="21" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1347" s="21" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1347" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1347" s="22" t="n">
+        <v>102955</v>
+      </c>
+      <c r="I1347" s="22" t="n">
+        <v>102955.1</v>
+      </c>
+      <c r="J1347" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1347" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1347" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1347" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1347" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1348" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1348" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1348" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1348" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1348" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1348" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1348" s="26" t="n">
+        <v>259010</v>
+      </c>
+      <c r="I1348" s="26" t="n">
+        <v>259010.24</v>
+      </c>
+      <c r="J1348" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1348" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1348" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1348" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1348" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1349" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1349" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1349" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1349" s="21" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1349" s="21" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1349" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1349" s="22" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I1349" s="22" t="n">
+        <v>1000000.93</v>
+      </c>
+      <c r="J1349" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1349" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1349" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1349" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1349" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1350" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1350" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1350" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1350" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1350" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1350" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1350" s="26" t="n">
+        <v>70200</v>
+      </c>
+      <c r="I1350" s="26" t="n">
+        <v>70200.07000000001</v>
+      </c>
+      <c r="J1350" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1350" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1350" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1350" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1350" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1351" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1351" s="20" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1351" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1351" s="21" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1351" s="21" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1351" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1351" s="22" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I1351" s="22" t="n">
+        <v>70000.06</v>
+      </c>
+      <c r="J1351" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1351" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1351" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1351" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1351" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="23" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1352" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1352" s="24" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1352" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1352" s="25" t="n">
+        <v>100.000093</v>
+      </c>
+      <c r="F1352" s="25" t="n">
+        <v>8.1137</v>
+      </c>
+      <c r="G1352" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1352" s="26" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I1352" s="26" t="n">
+        <v>7000.01</v>
+      </c>
+      <c r="J1352" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1352" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1352" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1352" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1352" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>

--- a/deuda-interna/deuda_interna_resumen.xlsx
+++ b/deuda-interna/deuda_interna_resumen.xlsx
@@ -604,7 +604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 12-Sep-2026  ·  Fuente: Bolsa de Valores de Quito</t>
+          <t>Generado: 09-Oct-2026  ·  Fuente: Bolsa de Valores de Quito</t>
         </is>
       </c>
     </row>
@@ -845,34 +845,34 @@
         <v>2026</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1970002216.109999</v>
+        <v>2021679208.999999</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>543538968.99</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1350282301.89</v>
+        <v>1398659374.819999</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>51407640.21999999</v>
+        <v>54707560.17999998</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>24773305.01</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>27.5907795709632</v>
+        <v>26.88552004543073</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>68.54217172183141</v>
+        <v>69.1830518211557</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>2.609521948737215</v>
+        <v>2.706045545527497</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1.257526758468211</v>
+        <v>1.225382587886129</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>7.74459457364341</v>
+        <v>7.79295501618123</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>4418645058.979999</v>
+        <v>4470322051.869998</v>
       </c>
       <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2400,19 +2400,44 @@
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>34169038.27000003</v>
+        <v>68462786.18000002</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>33777486.53000002</v>
+        <v>64871314.59000003</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>55000.17000000001</v>
+        <v>3254920.02</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>336551.57</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>17383244.98</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>17283244.87</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>100000.11</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3985,16 +4010,38 @@
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>4.8417</v>
+        <v>5.5724</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>7.5018</v>
+        <v>7.5001</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>8.331300000000001</v>
+        <v>8.159599999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>9.047599999999999</v>
+        <v>8.8202</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>7.7685</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>8.2723</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4011,7 +4058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1352"/>
+  <dimension ref="A1:N1454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -76985,6 +77032,5514 @@
         </is>
       </c>
     </row>
+    <row r="1353">
+      <c r="A1353" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1353" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1353" s="20" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D1353" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1353" s="21" t="n">
+        <v>100.000197</v>
+      </c>
+      <c r="F1353" s="21" t="n">
+        <v>8.1134</v>
+      </c>
+      <c r="G1353" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1353" s="22" t="n">
+        <v>70225</v>
+      </c>
+      <c r="I1353" s="22" t="n">
+        <v>70225.14</v>
+      </c>
+      <c r="J1353" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1353" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1353" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1353" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1353" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1354" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1354" s="24" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D1354" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1354" s="25" t="n">
+        <v>100.000058</v>
+      </c>
+      <c r="F1354" s="25" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="G1354" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1354" s="26" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I1354" s="26" t="n">
+        <v>1500000.87</v>
+      </c>
+      <c r="J1354" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1354" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1354" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1354" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1354" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1355" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1355" s="20" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D1355" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1355" s="21" t="n">
+        <v>100.000197</v>
+      </c>
+      <c r="F1355" s="21" t="n">
+        <v>8.1134</v>
+      </c>
+      <c r="G1355" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1355" s="22" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I1355" s="22" t="n">
+        <v>600001.1800000001</v>
+      </c>
+      <c r="J1355" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1355" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1355" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1355" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1355" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1356" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1356" s="24" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D1356" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1356" s="25" t="n">
+        <v>100.000197</v>
+      </c>
+      <c r="F1356" s="25" t="n">
+        <v>8.1134</v>
+      </c>
+      <c r="G1356" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1356" s="26" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I1356" s="26" t="n">
+        <v>3500006.9</v>
+      </c>
+      <c r="J1356" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1356" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1356" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1356" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1356" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1357" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1357" s="20" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D1357" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1357" s="21" t="n">
+        <v>100.000197</v>
+      </c>
+      <c r="F1357" s="21" t="n">
+        <v>8.1134</v>
+      </c>
+      <c r="G1357" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1357" s="22" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I1357" s="22" t="n">
+        <v>3500006.9</v>
+      </c>
+      <c r="J1357" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1357" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1357" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1357" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1357" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="23" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1358" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1358" s="24" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D1358" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1358" s="25" t="n">
+        <v>100.000058</v>
+      </c>
+      <c r="F1358" s="25" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="G1358" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1358" s="26" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I1358" s="26" t="n">
+        <v>1500000.87</v>
+      </c>
+      <c r="J1358" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1358" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1358" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1358" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1358" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="19" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1359" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1359" s="20" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1359" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1359" s="21" t="n">
+        <v>100.000241</v>
+      </c>
+      <c r="F1359" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1359" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1359" s="22" t="n">
+        <v>29550</v>
+      </c>
+      <c r="I1359" s="22" t="n">
+        <v>29550.07</v>
+      </c>
+      <c r="J1359" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1359" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1359" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1359" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1359" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1360" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1360" s="24" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1360" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1360" s="25" t="n">
+        <v>100.000241</v>
+      </c>
+      <c r="F1360" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1360" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1360" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1360" s="26" t="n">
+        <v>12000.03</v>
+      </c>
+      <c r="J1360" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1360" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1360" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1360" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1360" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="19" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1361" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1361" s="20" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1361" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1361" s="21" t="n">
+        <v>100.000241</v>
+      </c>
+      <c r="F1361" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1361" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1361" s="22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I1361" s="22" t="n">
+        <v>250000.6</v>
+      </c>
+      <c r="J1361" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1361" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1361" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1361" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1361" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="23" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1362" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1362" s="24" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D1362" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1362" s="25" t="n">
+        <v>100.000241</v>
+      </c>
+      <c r="F1362" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1362" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1362" s="26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I1362" s="26" t="n">
+        <v>70000.17</v>
+      </c>
+      <c r="J1362" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1362" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1362" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1362" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1362" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="19" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1363" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1363" s="20" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1363" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1363" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1363" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1363" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1363" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1363" s="22" t="n">
+        <v>30000.01</v>
+      </c>
+      <c r="J1363" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1363" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1363" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1363" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1363" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1364" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1364" s="24" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1364" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1364" s="25" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1364" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1364" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1364" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1364" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J1364" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1364" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1364" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1364" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1364" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="19" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1365" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1365" s="20" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1365" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1365" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1365" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1365" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1365" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1365" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J1365" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1365" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1365" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1365" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1365" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1366" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1366" s="24" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1366" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1366" s="25" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1366" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1366" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1366" s="26" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I1366" s="26" t="n">
+        <v>300000.12</v>
+      </c>
+      <c r="J1366" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1366" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1366" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1366" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1366" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="19" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1367" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1367" s="20" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1367" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1367" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1367" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1367" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1367" s="22" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I1367" s="22" t="n">
+        <v>28000.01</v>
+      </c>
+      <c r="J1367" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1367" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1367" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1367" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1367" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1368" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1368" s="24" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1368" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1368" s="25" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1368" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1368" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1368" s="26" t="n">
+        <v>8700</v>
+      </c>
+      <c r="I1368" s="26" t="n">
+        <v>8700</v>
+      </c>
+      <c r="J1368" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1368" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1368" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1368" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1368" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="19" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1369" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1369" s="20" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1369" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1369" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1369" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1369" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1369" s="22" t="n">
+        <v>60900</v>
+      </c>
+      <c r="I1369" s="22" t="n">
+        <v>60900.02</v>
+      </c>
+      <c r="J1369" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1369" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1369" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1369" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1369" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="23" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1370" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1370" s="24" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1370" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1370" s="25" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1370" s="25" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1370" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1370" s="26" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I1370" s="26" t="n">
+        <v>12500</v>
+      </c>
+      <c r="J1370" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1370" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1370" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1370" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1370" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="19" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1371" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1371" s="20" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D1371" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1371" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1371" s="21" t="n">
+        <v>8.113300000000001</v>
+      </c>
+      <c r="G1371" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1371" s="22" t="n">
+        <v>3937600.75</v>
+      </c>
+      <c r="I1371" s="22" t="n">
+        <v>3937602.28</v>
+      </c>
+      <c r="J1371" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1371" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1371" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1371" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1371" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1372" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1372" s="24" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D1372" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1372" s="25" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1372" s="25" t="n">
+        <v>8.113200000000001</v>
+      </c>
+      <c r="G1372" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1372" s="26" t="n">
+        <v>350000</v>
+      </c>
+      <c r="I1372" s="26" t="n">
+        <v>350000.32</v>
+      </c>
+      <c r="J1372" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1372" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1372" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1372" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1372" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="19" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1373" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1373" s="20" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D1373" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1373" s="21" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1373" s="21" t="n">
+        <v>8.113200000000001</v>
+      </c>
+      <c r="G1373" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1373" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1373" s="22" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1373" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1373" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1373" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1373" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1373" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1374" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1374" s="24" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D1374" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1374" s="25" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1374" s="25" t="n">
+        <v>8.113200000000001</v>
+      </c>
+      <c r="G1374" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1374" s="26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1374" s="26" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1374" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1374" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1374" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1374" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1374" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="19" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1375" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1375" s="20" t="n">
+        <v>670</v>
+      </c>
+      <c r="D1375" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1375" s="21" t="n">
+        <v>100.000125</v>
+      </c>
+      <c r="F1375" s="21" t="n">
+        <v>7.1925</v>
+      </c>
+      <c r="G1375" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1375" s="22" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1375" s="22" t="n">
+        <v>500000.63</v>
+      </c>
+      <c r="J1375" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1375" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1375" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1375" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1375" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="23" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1376" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1376" s="24" t="n">
+        <v>670</v>
+      </c>
+      <c r="D1376" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1376" s="25" t="n">
+        <v>100.000125</v>
+      </c>
+      <c r="F1376" s="25" t="n">
+        <v>7.1925</v>
+      </c>
+      <c r="G1376" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1376" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1376" s="26" t="n">
+        <v>500000.63</v>
+      </c>
+      <c r="J1376" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1376" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1376" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1376" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1376" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="19" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1377" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1377" s="20" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D1377" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1377" s="21" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1377" s="21" t="n">
+        <v>8.113200000000001</v>
+      </c>
+      <c r="G1377" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1377" s="22" t="n">
+        <v>55000</v>
+      </c>
+      <c r="I1377" s="22" t="n">
+        <v>55000.05</v>
+      </c>
+      <c r="J1377" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1377" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1377" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1377" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1377" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="23" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1378" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1378" s="24" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D1378" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1378" s="25" t="n">
+        <v>100.000149</v>
+      </c>
+      <c r="F1378" s="25" t="n">
+        <v>8.113099999999999</v>
+      </c>
+      <c r="G1378" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1378" s="26" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I1378" s="26" t="n">
+        <v>300000.45</v>
+      </c>
+      <c r="J1378" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1378" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1378" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1378" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1378" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="19" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1379" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1379" s="20" t="n">
+        <v>666</v>
+      </c>
+      <c r="D1379" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1379" s="21" t="n">
+        <v>100.000137</v>
+      </c>
+      <c r="F1379" s="21" t="n">
+        <v>7.1921</v>
+      </c>
+      <c r="G1379" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1379" s="22" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I1379" s="22" t="n">
+        <v>10000013.69</v>
+      </c>
+      <c r="J1379" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1379" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1379" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1379" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1379" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="23" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1380" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1380" s="24" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D1380" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1380" s="25" t="n">
+        <v>100.0001</v>
+      </c>
+      <c r="F1380" s="25" t="n">
+        <v>8.1129</v>
+      </c>
+      <c r="G1380" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1380" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1380" s="26" t="n">
+        <v>500000.5</v>
+      </c>
+      <c r="J1380" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1380" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1380" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1380" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1380" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="19" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1381" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1381" s="20" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D1381" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1381" s="21" t="n">
+        <v>100.0001</v>
+      </c>
+      <c r="F1381" s="21" t="n">
+        <v>8.1129</v>
+      </c>
+      <c r="G1381" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1381" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I1381" s="22" t="n">
+        <v>25000.02</v>
+      </c>
+      <c r="J1381" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1381" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1381" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1381" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1381" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1382" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1382" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1382" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1382" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1382" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1382" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1382" s="26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1382" s="26" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1382" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1382" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1382" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1382" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1382" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1383" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1383" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1383" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1383" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1383" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1383" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1383" s="22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1383" s="22" t="n">
+        <v>9000.02</v>
+      </c>
+      <c r="J1383" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1383" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1383" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1383" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1383" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1384" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1384" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1384" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1384" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1384" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1384" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1384" s="26" t="n">
+        <v>39296</v>
+      </c>
+      <c r="I1384" s="26" t="n">
+        <v>39296.07</v>
+      </c>
+      <c r="J1384" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1384" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1384" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1384" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1384" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1385" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1385" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1385" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1385" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1385" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1385" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1385" s="22" t="n">
+        <v>9776</v>
+      </c>
+      <c r="I1385" s="22" t="n">
+        <v>9776.02</v>
+      </c>
+      <c r="J1385" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1385" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1385" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1385" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1385" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1386" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1386" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1386" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1386" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1386" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1386" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1386" s="26" t="n">
+        <v>56100</v>
+      </c>
+      <c r="I1386" s="26" t="n">
+        <v>56100.1</v>
+      </c>
+      <c r="J1386" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1386" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1386" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1386" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1386" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1387" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1387" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1387" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1387" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1387" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1387" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1387" s="22" t="n">
+        <v>411082</v>
+      </c>
+      <c r="I1387" s="22" t="n">
+        <v>411082.72</v>
+      </c>
+      <c r="J1387" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1387" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1387" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1387" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1387" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1388" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1388" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1388" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1388" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1388" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1388" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1388" s="26" t="n">
+        <v>173505</v>
+      </c>
+      <c r="I1388" s="26" t="n">
+        <v>173505.3</v>
+      </c>
+      <c r="J1388" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1388" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1388" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1388" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1388" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1389" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1389" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1389" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1389" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1389" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1389" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1389" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1389" s="22" t="n">
+        <v>5000.01</v>
+      </c>
+      <c r="J1389" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1389" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1389" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1389" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1389" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1390" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1390" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1390" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1390" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1390" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1390" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1390" s="26" t="n">
+        <v>136586</v>
+      </c>
+      <c r="I1390" s="26" t="n">
+        <v>136586.24</v>
+      </c>
+      <c r="J1390" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1390" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1390" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1390" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1390" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1391" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1391" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1391" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1391" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1391" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1391" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1391" s="22" t="n">
+        <v>98545</v>
+      </c>
+      <c r="I1391" s="22" t="n">
+        <v>98545.17</v>
+      </c>
+      <c r="J1391" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1391" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1391" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1391" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1391" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1392" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1392" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1392" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1392" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1392" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1392" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1392" s="26" t="n">
+        <v>51000</v>
+      </c>
+      <c r="I1392" s="26" t="n">
+        <v>51000.09</v>
+      </c>
+      <c r="J1392" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1392" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1392" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1392" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1392" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="19" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1393" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1393" s="20" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1393" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1393" s="21" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1393" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1393" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1393" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1393" s="22" t="n">
+        <v>10000.02</v>
+      </c>
+      <c r="J1393" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1393" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1393" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1393" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1393" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="23" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1394" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1394" s="24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1394" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1394" s="25" t="n">
+        <v>100.000176</v>
+      </c>
+      <c r="F1394" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1394" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1394" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1394" s="26" t="n">
+        <v>30000.05</v>
+      </c>
+      <c r="J1394" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1394" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1394" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1394" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1394" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="19" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1395" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1395" s="20" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1395" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1395" s="21" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1395" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1395" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1395" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1395" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J1395" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1395" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1395" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1395" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1395" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1396" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1396" s="24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1396" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1396" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1396" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1396" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1396" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1396" s="26" t="n">
+        <v>500000.03</v>
+      </c>
+      <c r="J1396" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1396" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1396" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1396" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1396" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="19" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1397" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1397" s="20" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1397" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1397" s="21" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1397" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1397" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1397" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1397" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J1397" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1397" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1397" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1397" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1397" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1398" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1398" s="24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1398" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1398" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1398" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1398" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1398" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1398" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J1398" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1398" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1398" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1398" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1398" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="19" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1399" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1399" s="20" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1399" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1399" s="21" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1399" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1399" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1399" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I1399" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J1399" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1399" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1399" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1399" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1399" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1400" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1400" s="24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1400" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1400" s="25" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1400" s="25" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1400" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1400" s="26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1400" s="26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J1400" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1400" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1400" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1400" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1400" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="19" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1401" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1401" s="20" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D1401" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1401" s="21" t="n">
+        <v>100.000007</v>
+      </c>
+      <c r="F1401" s="21" t="n">
+        <v>8.1128</v>
+      </c>
+      <c r="G1401" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1401" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1401" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J1401" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1401" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1401" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1401" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1401" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1402" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1402" s="24" t="n">
+        <v>664</v>
+      </c>
+      <c r="D1402" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1402" s="25" t="n">
+        <v>100.000163</v>
+      </c>
+      <c r="F1402" s="25" t="n">
+        <v>7.1919</v>
+      </c>
+      <c r="G1402" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1402" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1402" s="26" t="n">
+        <v>500000.82</v>
+      </c>
+      <c r="J1402" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1402" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1402" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1402" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1402" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="19" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1403" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1403" s="20" t="n">
+        <v>664</v>
+      </c>
+      <c r="D1403" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1403" s="21" t="n">
+        <v>100.000163</v>
+      </c>
+      <c r="F1403" s="21" t="n">
+        <v>7.1919</v>
+      </c>
+      <c r="G1403" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1403" s="22" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I1403" s="22" t="n">
+        <v>400000.65</v>
+      </c>
+      <c r="J1403" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1403" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1403" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1403" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1403" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="23" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1404" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1404" s="24" t="n">
+        <v>1746</v>
+      </c>
+      <c r="D1404" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1404" s="25" t="n">
+        <v>100.000059</v>
+      </c>
+      <c r="F1404" s="25" t="n">
+        <v>8.285500000000001</v>
+      </c>
+      <c r="G1404" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1404" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I1404" s="26" t="n">
+        <v>60000.04</v>
+      </c>
+      <c r="J1404" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1404" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1404" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1404" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1404" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="19" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1405" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1405" s="20" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1405" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1405" s="21" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1405" s="21" t="n">
+        <v>8.1127</v>
+      </c>
+      <c r="G1405" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1405" s="22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1405" s="22" t="n">
+        <v>9000.01</v>
+      </c>
+      <c r="J1405" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1405" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1405" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1405" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1405" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="23" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1406" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1406" s="24" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1406" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1406" s="25" t="n">
+        <v>100.000092</v>
+      </c>
+      <c r="F1406" s="25" t="n">
+        <v>8.1127</v>
+      </c>
+      <c r="G1406" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1406" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1406" s="26" t="n">
+        <v>30000.03</v>
+      </c>
+      <c r="J1406" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1406" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1406" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1406" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1406" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="19" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1407" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1407" s="20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1407" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1407" s="21" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1407" s="21" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1407" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1407" s="22" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I1407" s="22" t="n">
+        <v>27000.05</v>
+      </c>
+      <c r="J1407" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1407" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1407" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1407" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1407" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="23" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1408" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1408" s="24" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1408" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1408" s="25" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1408" s="25" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1408" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1408" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1408" s="26" t="n">
+        <v>30000.05</v>
+      </c>
+      <c r="J1408" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1408" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1408" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1408" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1408" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="19" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1409" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1409" s="20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1409" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1409" s="21" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1409" s="21" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1409" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1409" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1409" s="22" t="n">
+        <v>6000.01</v>
+      </c>
+      <c r="J1409" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1409" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1409" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1409" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1409" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="23" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1410" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1410" s="24" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1410" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1410" s="25" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1410" s="25" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1410" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1410" s="26" t="n">
+        <v>191483</v>
+      </c>
+      <c r="I1410" s="26" t="n">
+        <v>191483.35</v>
+      </c>
+      <c r="J1410" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1410" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1410" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1410" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1410" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="19" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1411" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1411" s="20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1411" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1411" s="21" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1411" s="21" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1411" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1411" s="22" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I1411" s="22" t="n">
+        <v>43000.08</v>
+      </c>
+      <c r="J1411" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1411" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1411" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1411" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1411" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="23" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1412" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1412" s="24" t="n">
+        <v>659</v>
+      </c>
+      <c r="D1412" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1412" s="25" t="n">
+        <v>100.00012</v>
+      </c>
+      <c r="F1412" s="25" t="n">
+        <v>7.1915</v>
+      </c>
+      <c r="G1412" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1412" s="26" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I1412" s="26" t="n">
+        <v>2000002.41</v>
+      </c>
+      <c r="J1412" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1412" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1412" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1412" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1412" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="19" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1413" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1413" s="20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1413" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1413" s="21" t="n">
+        <v>100.000182</v>
+      </c>
+      <c r="F1413" s="21" t="n">
+        <v>8.1126</v>
+      </c>
+      <c r="G1413" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1413" s="22" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1413" s="22" t="n">
+        <v>500000.91</v>
+      </c>
+      <c r="J1413" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1413" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1413" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1413" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1413" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1414" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1414" s="24" t="n">
+        <v>1741</v>
+      </c>
+      <c r="D1414" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1414" s="25" t="n">
+        <v>100.000319</v>
+      </c>
+      <c r="F1414" s="25" t="n">
+        <v>8.2852</v>
+      </c>
+      <c r="G1414" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1414" s="26" t="n">
+        <v>139917.62</v>
+      </c>
+      <c r="I1414" s="26" t="n">
+        <v>139918.07</v>
+      </c>
+      <c r="J1414" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1414" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1414" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1414" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1414" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="19" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1415" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1415" s="20" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1415" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1415" s="21" t="n">
+        <v>100.00023</v>
+      </c>
+      <c r="F1415" s="21" t="n">
+        <v>8.112399999999999</v>
+      </c>
+      <c r="G1415" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1415" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1415" s="22" t="n">
+        <v>10000.02</v>
+      </c>
+      <c r="J1415" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1415" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1415" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1415" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1415" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1416" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1416" s="24" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1416" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1416" s="25" t="n">
+        <v>100.00023</v>
+      </c>
+      <c r="F1416" s="25" t="n">
+        <v>8.112399999999999</v>
+      </c>
+      <c r="G1416" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1416" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1416" s="26" t="n">
+        <v>10000.02</v>
+      </c>
+      <c r="J1416" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1416" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1416" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1416" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1416" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="19" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1417" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1417" s="20" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1417" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1417" s="21" t="n">
+        <v>100.00023</v>
+      </c>
+      <c r="F1417" s="21" t="n">
+        <v>8.112399999999999</v>
+      </c>
+      <c r="G1417" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1417" s="22" t="n">
+        <v>19605</v>
+      </c>
+      <c r="I1417" s="22" t="n">
+        <v>19605.05</v>
+      </c>
+      <c r="J1417" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1417" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1417" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1417" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1417" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1418" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1418" s="24" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D1418" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1418" s="25" t="n">
+        <v>100.00023</v>
+      </c>
+      <c r="F1418" s="25" t="n">
+        <v>8.112399999999999</v>
+      </c>
+      <c r="G1418" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1418" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1418" s="26" t="n">
+        <v>10000.02</v>
+      </c>
+      <c r="J1418" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1418" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1418" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1418" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1418" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="19" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1419" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1419" s="20" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D1419" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1419" s="21" t="n">
+        <v>100.000202</v>
+      </c>
+      <c r="F1419" s="21" t="n">
+        <v>8.112299999999999</v>
+      </c>
+      <c r="G1419" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1419" s="22" t="n">
+        <v>985331</v>
+      </c>
+      <c r="I1419" s="22" t="n">
+        <v>985332.99</v>
+      </c>
+      <c r="J1419" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1419" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1419" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1419" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1419" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="23" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1420" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1420" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D1420" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1420" s="25" t="n">
+        <v>100.000072</v>
+      </c>
+      <c r="F1420" s="25" t="n">
+        <v>8.112299999999999</v>
+      </c>
+      <c r="G1420" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1420" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1420" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J1420" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1420" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1420" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1420" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1420" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="19" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1421" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1421" s="20" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D1421" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1421" s="21" t="n">
+        <v>100.000072</v>
+      </c>
+      <c r="F1421" s="21" t="n">
+        <v>8.112299999999999</v>
+      </c>
+      <c r="G1421" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1421" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I1421" s="22" t="n">
+        <v>200000.14</v>
+      </c>
+      <c r="J1421" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1421" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1421" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1421" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1421" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="23" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1422" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1422" s="24" t="n">
+        <v>1738</v>
+      </c>
+      <c r="D1422" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1422" s="25" t="n">
+        <v>100.000222</v>
+      </c>
+      <c r="F1422" s="25" t="n">
+        <v>8.2851</v>
+      </c>
+      <c r="G1422" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1422" s="26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I1422" s="26" t="n">
+        <v>40000.09</v>
+      </c>
+      <c r="J1422" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1422" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1422" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1422" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1422" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="19" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1423" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1423" s="20" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1423" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1423" s="21" t="n">
+        <v>100.000194</v>
+      </c>
+      <c r="F1423" s="21" t="n">
+        <v>8.1122</v>
+      </c>
+      <c r="G1423" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1423" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1423" s="22" t="n">
+        <v>30000.06</v>
+      </c>
+      <c r="J1423" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1423" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1423" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1423" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1423" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="23" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1424" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1424" s="24" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D1424" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1424" s="25" t="n">
+        <v>100.000069</v>
+      </c>
+      <c r="F1424" s="25" t="n">
+        <v>8.2851</v>
+      </c>
+      <c r="G1424" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1424" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1424" s="26" t="n">
+        <v>10000.01</v>
+      </c>
+      <c r="J1424" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1424" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1424" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1424" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1424" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="19" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1425" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1425" s="20" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1425" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1425" s="21" t="n">
+        <v>100.000194</v>
+      </c>
+      <c r="F1425" s="21" t="n">
+        <v>8.1122</v>
+      </c>
+      <c r="G1425" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1425" s="22" t="n">
+        <v>144575</v>
+      </c>
+      <c r="I1425" s="22" t="n">
+        <v>144575.28</v>
+      </c>
+      <c r="J1425" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1425" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1425" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1425" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1425" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="23" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1426" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1426" s="24" t="n">
+        <v>655</v>
+      </c>
+      <c r="D1426" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1426" s="25" t="n">
+        <v>100.000116</v>
+      </c>
+      <c r="F1426" s="25" t="n">
+        <v>7.1912</v>
+      </c>
+      <c r="G1426" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1426" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1426" s="26" t="n">
+        <v>5000.01</v>
+      </c>
+      <c r="J1426" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1426" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1426" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1426" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1426" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="19" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1427" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1427" s="20" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1427" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1427" s="21" t="n">
+        <v>100.000194</v>
+      </c>
+      <c r="F1427" s="21" t="n">
+        <v>8.1122</v>
+      </c>
+      <c r="G1427" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1427" s="22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I1427" s="22" t="n">
+        <v>80000.16</v>
+      </c>
+      <c r="J1427" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1427" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1427" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1427" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1427" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="23" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1428" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1428" s="24" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D1428" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1428" s="25" t="n">
+        <v>100.000194</v>
+      </c>
+      <c r="F1428" s="25" t="n">
+        <v>8.1122</v>
+      </c>
+      <c r="G1428" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1428" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1428" s="26" t="n">
+        <v>15000.03</v>
+      </c>
+      <c r="J1428" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1428" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1428" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1428" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1428" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="19" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1429" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1429" s="20" t="n">
+        <v>1734</v>
+      </c>
+      <c r="D1429" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1429" s="21" t="n">
+        <v>100.000032</v>
+      </c>
+      <c r="F1429" s="21" t="n">
+        <v>8.285</v>
+      </c>
+      <c r="G1429" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1429" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1429" s="22" t="n">
+        <v>30000.01</v>
+      </c>
+      <c r="J1429" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1429" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1429" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1429" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1429" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="23" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1430" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1430" s="24" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1430" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1430" s="25" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1430" s="25" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1430" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1430" s="26" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I1430" s="26" t="n">
+        <v>3000002.83</v>
+      </c>
+      <c r="J1430" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1430" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1430" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1430" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1430" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="19" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1431" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1431" s="20" t="n">
+        <v>1734</v>
+      </c>
+      <c r="D1431" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1431" s="21" t="n">
+        <v>100.000032</v>
+      </c>
+      <c r="F1431" s="21" t="n">
+        <v>8.285</v>
+      </c>
+      <c r="G1431" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1431" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1431" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J1431" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1431" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1431" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1431" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1431" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="23" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1432" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1432" s="24" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1432" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1432" s="25" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1432" s="25" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1432" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1432" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1432" s="26" t="n">
+        <v>10000.01</v>
+      </c>
+      <c r="J1432" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1432" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1432" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1432" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1432" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="19" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1433" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1433" s="20" t="n">
+        <v>1734</v>
+      </c>
+      <c r="D1433" s="15" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1433" s="21" t="n">
+        <v>100.000032</v>
+      </c>
+      <c r="F1433" s="21" t="n">
+        <v>8.285</v>
+      </c>
+      <c r="G1433" s="21" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1433" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1433" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J1433" s="19" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1433" s="19" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1433" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1433" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1433" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="23" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1434" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1434" s="24" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1434" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1434" s="25" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1434" s="25" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1434" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1434" s="26" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I1434" s="26" t="n">
+        <v>2000001.89</v>
+      </c>
+      <c r="J1434" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1434" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1434" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1434" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1434" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="19" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1435" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1435" s="20" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1435" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1435" s="21" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1435" s="21" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1435" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1435" s="22" t="n">
+        <v>29370</v>
+      </c>
+      <c r="I1435" s="22" t="n">
+        <v>29370.03</v>
+      </c>
+      <c r="J1435" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1435" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1435" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1435" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1435" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="23" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1436" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1436" s="24" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1436" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1436" s="25" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1436" s="25" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1436" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1436" s="26" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I1436" s="26" t="n">
+        <v>6000005.66</v>
+      </c>
+      <c r="J1436" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1436" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1436" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1436" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1436" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="19" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1437" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1437" s="20" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1437" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1437" s="21" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1437" s="21" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1437" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1437" s="22" t="n">
+        <v>51000</v>
+      </c>
+      <c r="I1437" s="22" t="n">
+        <v>51000.05</v>
+      </c>
+      <c r="J1437" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1437" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1437" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1437" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1437" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="23" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1438" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1438" s="24" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D1438" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1438" s="25" t="n">
+        <v>100.000094</v>
+      </c>
+      <c r="F1438" s="25" t="n">
+        <v>8.1121</v>
+      </c>
+      <c r="G1438" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1438" s="26" t="n">
+        <v>30800</v>
+      </c>
+      <c r="I1438" s="26" t="n">
+        <v>30800.03</v>
+      </c>
+      <c r="J1438" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1438" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1438" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1438" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1438" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="19" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1439" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1439" s="20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1439" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1439" s="21" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1439" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1439" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1439" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I1439" s="22" t="n">
+        <v>40000.09</v>
+      </c>
+      <c r="J1439" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1439" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1439" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1439" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1439" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1440" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1440" s="24" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1440" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1440" s="25" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1440" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1440" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1440" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I1440" s="26" t="n">
+        <v>20000.05</v>
+      </c>
+      <c r="J1440" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1440" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1440" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1440" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1440" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="19" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1441" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1441" s="20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1441" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1441" s="21" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1441" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1441" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1441" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1441" s="22" t="n">
+        <v>5000.01</v>
+      </c>
+      <c r="J1441" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1441" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1441" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1441" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1441" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1442" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1442" s="24" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1442" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1442" s="25" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1442" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1442" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1442" s="26" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I1442" s="26" t="n">
+        <v>4000009.39</v>
+      </c>
+      <c r="J1442" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1442" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1442" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1442" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1442" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="19" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1443" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1443" s="20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1443" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1443" s="21" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1443" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1443" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1443" s="22" t="n">
+        <v>50850</v>
+      </c>
+      <c r="I1443" s="22" t="n">
+        <v>50850.12</v>
+      </c>
+      <c r="J1443" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1443" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1443" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1443" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1443" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1444" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1444" s="24" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1444" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1444" s="25" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1444" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1444" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1444" s="26" t="n">
+        <v>299930</v>
+      </c>
+      <c r="I1444" s="26" t="n">
+        <v>299930.7</v>
+      </c>
+      <c r="J1444" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1444" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1444" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1444" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1444" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="19" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1445" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1445" s="20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1445" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1445" s="21" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1445" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1445" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1445" s="22" t="n">
+        <v>196480</v>
+      </c>
+      <c r="I1445" s="22" t="n">
+        <v>196480.46</v>
+      </c>
+      <c r="J1445" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1445" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1445" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1445" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1445" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1446" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1446" s="24" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1446" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1446" s="25" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1446" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1446" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1446" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1446" s="26" t="n">
+        <v>5000.01</v>
+      </c>
+      <c r="J1446" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1446" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1446" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1446" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1446" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="19" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1447" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1447" s="20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D1447" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1447" s="21" t="n">
+        <v>100.000235</v>
+      </c>
+      <c r="F1447" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1447" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1447" s="22" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I1447" s="22" t="n">
+        <v>15600.04</v>
+      </c>
+      <c r="J1447" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1447" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1447" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1447" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1447" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1448" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1448" s="24" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1448" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1448" s="25" t="n">
+        <v>100.000134</v>
+      </c>
+      <c r="F1448" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1448" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1448" s="26" t="n">
+        <v>29360</v>
+      </c>
+      <c r="I1448" s="26" t="n">
+        <v>29360.04</v>
+      </c>
+      <c r="J1448" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1448" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1448" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1448" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1448" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="19" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1449" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1449" s="20" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1449" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1449" s="21" t="n">
+        <v>100.000134</v>
+      </c>
+      <c r="F1449" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1449" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1449" s="22" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I1449" s="22" t="n">
+        <v>130000.17</v>
+      </c>
+      <c r="J1449" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1449" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1449" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1449" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1449" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1450" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1450" s="24" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1450" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1450" s="25" t="n">
+        <v>100.000134</v>
+      </c>
+      <c r="F1450" s="25" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1450" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1450" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1450" s="26" t="n">
+        <v>12000.02</v>
+      </c>
+      <c r="J1450" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1450" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1450" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1450" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1450" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="19" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1451" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1451" s="20" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D1451" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1451" s="21" t="n">
+        <v>100.000134</v>
+      </c>
+      <c r="F1451" s="21" t="n">
+        <v>8.112</v>
+      </c>
+      <c r="G1451" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1451" s="22" t="n">
+        <v>28257</v>
+      </c>
+      <c r="I1451" s="22" t="n">
+        <v>28257.04</v>
+      </c>
+      <c r="J1451" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1451" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1451" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1451" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1451" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1452" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1452" s="24" t="n">
+        <v>650</v>
+      </c>
+      <c r="D1452" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1452" s="25" t="n">
+        <v>100.000065</v>
+      </c>
+      <c r="F1452" s="25" t="n">
+        <v>7.1909</v>
+      </c>
+      <c r="G1452" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1452" s="26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I1452" s="26" t="n">
+        <v>150000.1</v>
+      </c>
+      <c r="J1452" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1452" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1452" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1452" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1452" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="19" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1453" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1453" s="20" t="n">
+        <v>650</v>
+      </c>
+      <c r="D1453" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1453" s="21" t="n">
+        <v>100.000065</v>
+      </c>
+      <c r="F1453" s="21" t="n">
+        <v>7.1909</v>
+      </c>
+      <c r="G1453" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1453" s="22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I1453" s="22" t="n">
+        <v>200000.13</v>
+      </c>
+      <c r="J1453" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1453" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1453" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1453" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1453" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1454" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1454" s="24" t="n">
+        <v>650</v>
+      </c>
+      <c r="D1454" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1454" s="25" t="n">
+        <v>100.000065</v>
+      </c>
+      <c r="F1454" s="25" t="n">
+        <v>7.1909</v>
+      </c>
+      <c r="G1454" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1454" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1454" s="26" t="n">
+        <v>500000.32</v>
+      </c>
+      <c r="J1454" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1454" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1454" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1454" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1454" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>

--- a/deuda-interna/deuda_interna_resumen.xlsx
+++ b/deuda-interna/deuda_interna_resumen.xlsx
@@ -604,7 +604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09-Oct-2026  ·  Fuente: Bolsa de Valores de Quito</t>
+          <t>Generado: 20-Oct-2026  ·  Fuente: Bolsa de Valores de Quito</t>
         </is>
       </c>
     </row>
@@ -845,34 +845,34 @@
         <v>2026</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>2021679208.999999</v>
+        <v>2053441209.959998</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>543538968.99</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1398659374.819999</v>
+        <v>1430409375.759999</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>54707560.17999998</v>
+        <v>54719560.19999999</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>24773305.01</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>26.88552004543073</v>
+        <v>26.46966303946868</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>69.1830518211557</v>
+        <v>69.65913456990882</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>2.706045545527497</v>
+        <v>2.664773646042974</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1.225382587886129</v>
+        <v>1.206428744579573</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>7.79295501618123</v>
+        <v>7.79986609375</v>
       </c>
     </row>
     <row r="10">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>4470322051.869998</v>
+        <v>4502084052.829998</v>
       </c>
       <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
@@ -2425,16 +2425,16 @@
         </is>
       </c>
       <c r="C61" s="9" t="n">
-        <v>17383244.98</v>
+        <v>49145245.94</v>
       </c>
       <c r="D61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>17283244.87</v>
+        <v>49033245.80999999</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>100000.11</v>
+        <v>112000.13</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>0</v>
@@ -4032,16 +4032,16 @@
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>5</v>
+        <v>5.4837</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>7.7685</v>
+        <v>7.5379</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>8.2723</v>
+        <v>8.293900000000001</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>9</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4058,7 +4058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1454"/>
+  <dimension ref="A1:N1476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82540,6 +82540,1194 @@
         </is>
       </c>
     </row>
+    <row r="1455">
+      <c r="A1455" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1455" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1455" s="20" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D1455" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1455" s="21" t="n">
+        <v>100.000193</v>
+      </c>
+      <c r="F1455" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1455" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1455" s="22" t="n">
+        <v>29400</v>
+      </c>
+      <c r="I1455" s="22" t="n">
+        <v>29400.06</v>
+      </c>
+      <c r="J1455" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1455" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1455" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1455" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1455" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="23" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1456" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1456" s="24" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D1456" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1456" s="25" t="n">
+        <v>100.000193</v>
+      </c>
+      <c r="F1456" s="25" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1456" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1456" s="26" t="n">
+        <v>14900</v>
+      </c>
+      <c r="I1456" s="26" t="n">
+        <v>14900.03</v>
+      </c>
+      <c r="J1456" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1456" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1456" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1456" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1456" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="19" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1457" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1457" s="20" t="n">
+        <v>645</v>
+      </c>
+      <c r="D1457" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1457" s="21" t="n">
+        <v>100.000104</v>
+      </c>
+      <c r="F1457" s="21" t="n">
+        <v>7.1906</v>
+      </c>
+      <c r="G1457" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1457" s="22" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I1457" s="22" t="n">
+        <v>400000.42</v>
+      </c>
+      <c r="J1457" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1457" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1457" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1457" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1457" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1458" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1458" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1458" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1458" s="25" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1458" s="25" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1458" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1458" s="26" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I1458" s="26" t="n">
+        <v>2000002.43</v>
+      </c>
+      <c r="J1458" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1458" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1458" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1458" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1458" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1459" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1459" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1459" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1459" s="21" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1459" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1459" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1459" s="22" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I1459" s="22" t="n">
+        <v>6000007.28</v>
+      </c>
+      <c r="J1459" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1459" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1459" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1459" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1459" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1460" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1460" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1460" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1460" s="25" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1460" s="25" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1460" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1460" s="26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I1460" s="26" t="n">
+        <v>500000.61</v>
+      </c>
+      <c r="J1460" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1460" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1460" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1460" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1460" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1461" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1461" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1461" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1461" s="21" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1461" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1461" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1461" s="22" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="I1461" s="22" t="n">
+        <v>1300001.58</v>
+      </c>
+      <c r="J1461" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1461" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1461" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1461" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1461" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1462" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1462" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1462" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1462" s="25" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1462" s="25" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1462" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1462" s="26" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="I1462" s="26" t="n">
+        <v>1100001.33</v>
+      </c>
+      <c r="J1462" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1462" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1462" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1462" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1462" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1463" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1463" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1463" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1463" s="21" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1463" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1463" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1463" s="22" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="I1463" s="22" t="n">
+        <v>1100001.33</v>
+      </c>
+      <c r="J1463" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1463" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1463" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1463" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1463" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="23" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1464" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1464" s="24" t="n">
+        <v>644</v>
+      </c>
+      <c r="D1464" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1464" s="25" t="n">
+        <v>100.000023</v>
+      </c>
+      <c r="F1464" s="25" t="n">
+        <v>7.1906</v>
+      </c>
+      <c r="G1464" s="25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1464" s="26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I1464" s="26" t="n">
+        <v>50000.01</v>
+      </c>
+      <c r="J1464" s="23" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1464" s="23" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1464" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1464" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1464" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="19" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1465" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1465" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D1465" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1465" s="21" t="n">
+        <v>100.000121</v>
+      </c>
+      <c r="F1465" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1465" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1465" s="22" t="n">
+        <v>2066779.4</v>
+      </c>
+      <c r="I1465" s="22" t="n">
+        <v>2066781.91</v>
+      </c>
+      <c r="J1465" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1465" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1465" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1465" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1465" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1466" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1466" s="24" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D1466" s="16" t="inlineStr">
+        <is>
+          <t>De 3 a 5</t>
+        </is>
+      </c>
+      <c r="E1466" s="25" t="n">
+        <v>100.000193</v>
+      </c>
+      <c r="F1466" s="25" t="n">
+        <v>8.284700000000001</v>
+      </c>
+      <c r="G1466" s="25" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H1466" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1466" s="26" t="n">
+        <v>12000.02</v>
+      </c>
+      <c r="J1466" s="23" t="n">
+        <v>46232</v>
+      </c>
+      <c r="K1466" s="23" t="n">
+        <v>48058</v>
+      </c>
+      <c r="L1466" s="16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1466" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1466" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1467" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1467" s="20" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1467" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1467" s="21" t="n">
+        <v>100.000055</v>
+      </c>
+      <c r="F1467" s="21" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1467" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1467" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I1467" s="22" t="n">
+        <v>15000.01</v>
+      </c>
+      <c r="J1467" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1467" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1467" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1467" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1467" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="23" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1468" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1468" s="24" t="n">
+        <v>999</v>
+      </c>
+      <c r="D1468" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1468" s="25" t="n">
+        <v>100.000055</v>
+      </c>
+      <c r="F1468" s="25" t="n">
+        <v>8.111800000000001</v>
+      </c>
+      <c r="G1468" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1468" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1468" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J1468" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1468" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1468" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1468" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1468" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="19" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1469" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1469" s="20" t="n">
+        <v>998</v>
+      </c>
+      <c r="D1469" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1469" s="21" t="n">
+        <v>100.000237</v>
+      </c>
+      <c r="F1469" s="21" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1469" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1469" s="22" t="n">
+        <v>58750</v>
+      </c>
+      <c r="I1469" s="22" t="n">
+        <v>58750.14</v>
+      </c>
+      <c r="J1469" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1469" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1469" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1469" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1469" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1470" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1470" s="24" t="n">
+        <v>998</v>
+      </c>
+      <c r="D1470" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1470" s="25" t="n">
+        <v>100.000237</v>
+      </c>
+      <c r="F1470" s="25" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1470" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1470" s="26" t="n">
+        <v>31140</v>
+      </c>
+      <c r="I1470" s="26" t="n">
+        <v>31140.07</v>
+      </c>
+      <c r="J1470" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1470" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1470" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1470" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1470" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="19" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1471" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1471" s="20" t="n">
+        <v>642</v>
+      </c>
+      <c r="D1471" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1471" s="21" t="n">
+        <v>100.000039</v>
+      </c>
+      <c r="F1471" s="21" t="n">
+        <v>7.1905</v>
+      </c>
+      <c r="G1471" s="21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H1471" s="22" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="I1471" s="22" t="n">
+        <v>7000002.74</v>
+      </c>
+      <c r="J1471" s="19" t="n">
+        <v>46230</v>
+      </c>
+      <c r="K1471" s="19" t="n">
+        <v>46961</v>
+      </c>
+      <c r="L1471" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1471" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1471" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="23" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1472" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1472" s="24" t="n">
+        <v>998</v>
+      </c>
+      <c r="D1472" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1472" s="25" t="n">
+        <v>100.000237</v>
+      </c>
+      <c r="F1472" s="25" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1472" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1472" s="26" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I1472" s="26" t="n">
+        <v>5000011.85</v>
+      </c>
+      <c r="J1472" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1472" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1472" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1472" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1472" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="19" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1473" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1473" s="20" t="n">
+        <v>997</v>
+      </c>
+      <c r="D1473" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1473" s="21" t="n">
+        <v>100.00018</v>
+      </c>
+      <c r="F1473" s="21" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1473" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1473" s="22" t="n">
+        <v>19540</v>
+      </c>
+      <c r="I1473" s="22" t="n">
+        <v>19540.04</v>
+      </c>
+      <c r="J1473" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1473" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1473" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1473" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1473" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1474" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1474" s="24" t="n">
+        <v>997</v>
+      </c>
+      <c r="D1474" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1474" s="25" t="n">
+        <v>100.00018</v>
+      </c>
+      <c r="F1474" s="25" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1474" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1474" s="26" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I1474" s="26" t="n">
+        <v>5000009</v>
+      </c>
+      <c r="J1474" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1474" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1474" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1474" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1474" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="19" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1475" s="15" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1475" s="20" t="n">
+        <v>997</v>
+      </c>
+      <c r="D1475" s="15" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1475" s="21" t="n">
+        <v>100.00018</v>
+      </c>
+      <c r="F1475" s="21" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1475" s="21" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1475" s="22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I1475" s="22" t="n">
+        <v>30000.05</v>
+      </c>
+      <c r="J1475" s="19" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1475" s="19" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1475" s="15" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1475" s="15" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1475" s="15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="23" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1476" s="16" t="inlineStr">
+        <is>
+          <t>2026-005</t>
+        </is>
+      </c>
+      <c r="C1476" s="24" t="n">
+        <v>997</v>
+      </c>
+      <c r="D1476" s="16" t="inlineStr">
+        <is>
+          <t>De 1 a 3</t>
+        </is>
+      </c>
+      <c r="E1476" s="25" t="n">
+        <v>100.00018</v>
+      </c>
+      <c r="F1476" s="25" t="n">
+        <v>8.111700000000001</v>
+      </c>
+      <c r="G1476" s="25" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H1476" s="26" t="n">
+        <v>26450</v>
+      </c>
+      <c r="I1476" s="26" t="n">
+        <v>26450.05</v>
+      </c>
+      <c r="J1476" s="23" t="n">
+        <v>46226</v>
+      </c>
+      <c r="K1476" s="23" t="n">
+        <v>47322</v>
+      </c>
+      <c r="L1476" s="16" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="M1476" s="16" t="inlineStr">
+        <is>
+          <t>UNIC</t>
+        </is>
+      </c>
+      <c r="N1476" s="16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
